--- a/Project/Slots/H999_幸運王牌2/Record/H999192_2608041410_betmode0_100000_8892_oldhand_card.xlsx
+++ b/Project/Slots/H999_幸運王牌2/Record/H999192_2608041410_betmode0_100000_8892_oldhand_card.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>幸運王牌</t>
+          <t>幸運王牌2</t>
         </is>
       </c>
     </row>
